--- a/Exam/gymtrackerpro/app/admin/workout-sessions/[id]/edit/_components/__tests__/ft/edit-workout-session-form/edit-workout-session-form-ft-form.xlsx
+++ b/Exam/gymtrackerpro/app/admin/workout-sessions/[id]/edit/_components/__tests__/ft/edit-workout-session-form/edit-workout-session-form-ft-form.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="109">
   <si>
     <t>Component: EditWorkoutSessionForm — EditWorkoutSessionForm - edits session metadata and exercise rows, refreshes after successful update, and deletes sessions back to the member page.</t>
   </si>
@@ -63,18 +63,6 @@
     <t>Successful update calls router.refresh(); successful delete calls router.refresh() and router.push(`/admin/members/${session.memberId}`).</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Run: npx jest edit-workout-session-form.test.tsx --selectProjects jsdom</t>
-  </si>
-  <si>
-    <t>Suite is kept in a single main describe block and covers metadata validation predicates, row mutation branches, server action outcomes, and pending UI state.</t>
-  </si>
-  <si>
-    <t>The form uses noValidate so client schema validation, rather than browser constraint validation, is exercised in JSDOM.</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -171,12 +159,24 @@
     <t>Type 1025 characters into Notes.</t>
   </si>
   <si>
-    <t>Validation failed alert visible; update action not called.</t>
+    <t>Validation failed alert and Notes max-length field error visible; update action not called.</t>
   </si>
   <si>
     <t>TC-07</t>
   </si>
   <si>
+    <t>Rejects an invalid exercise row and does not call update.</t>
+  </si>
+  <si>
+    <t>Clear Exercise and set sets/reps/weight above their upper bounds.</t>
+  </si>
+  <si>
+    <t>Validation failed plus Exercise, Sets, Reps, and Weight field errors are visible; update action not called.</t>
+  </si>
+  <si>
+    <t>TC-08</t>
+  </si>
+  <si>
     <t>Adds a second exercise row and enables removal.</t>
   </si>
   <si>
@@ -189,7 +189,7 @@
     <t>Two exercise selects and two Remove buttons exist; the first Remove is enabled.</t>
   </si>
   <si>
-    <t>TC-08</t>
+    <t>TC-09</t>
   </si>
   <si>
     <t>Removes the second exercise row and disables the remaining Remove button.</t>
@@ -204,7 +204,7 @@
     <t>One exercise select remains and the sole Remove button is disabled.</t>
   </si>
   <si>
-    <t>TC-09</t>
+    <t>TC-10</t>
   </si>
   <si>
     <t>Calls update action with edited metadata and parsed existing row, then refreshes.</t>
@@ -216,7 +216,7 @@
     <t>Success alert visible; update action called with trimmed notes and numeric row values; refresh called once; push not called.</t>
   </si>
   <si>
-    <t>TC-10</t>
+    <t>TC-11</t>
   </si>
   <si>
     <t>Submits a newly added row without an existing row ID.</t>
@@ -228,7 +228,7 @@
     <t>update action receives the original row plus a new parsed row with id undefined.</t>
   </si>
   <si>
-    <t>TC-11</t>
+    <t>TC-12</t>
   </si>
   <si>
     <t>Shows server error and does not refresh when update fails.</t>
@@ -240,7 +240,7 @@
     <t>Server error visible; Save Changes enabled; refresh and push not called.</t>
   </si>
   <si>
-    <t>TC-12</t>
+    <t>TC-13</t>
   </si>
   <si>
     <t>Displays returned server field errors for editable metadata.</t>
@@ -252,7 +252,7 @@
     <t>Validation failed alert plus returned date and duration errors are visible; refresh not called.</t>
   </si>
   <si>
-    <t>TC-13</t>
+    <t>TC-14</t>
   </si>
   <si>
     <t>Deletes session, refreshes, and navigates to member detail.</t>
@@ -267,7 +267,7 @@
     <t>delete called with session-1; refresh called; router.push /admin/members/mem-1.</t>
   </si>
   <si>
-    <t>TC-14</t>
+    <t>TC-15</t>
   </si>
   <si>
     <t>Shows delete error and does not navigate or refresh when delete fails.</t>
@@ -279,7 +279,7 @@
     <t>Server error visible; delete called once; router.push and refresh not called.</t>
   </si>
   <si>
-    <t>TC-15</t>
+    <t>TC-16</t>
   </si>
   <si>
     <t>Disables save and delete controls while update is pending.</t>
@@ -780,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -869,50 +869,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -921,7 +882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -936,22 +897,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -959,22 +920,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="G2" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -982,22 +943,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1005,22 +966,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1028,22 +989,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,45 +1012,45 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1097,22 +1058,22 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1120,22 +1081,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1143,22 +1104,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1166,68 +1127,68 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="G12" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="G13" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1235,22 +1196,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1258,22 +1219,22 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1281,22 +1242,45 @@
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>31</v>
+      <c r="G17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1392,10 +1376,10 @@
         <v>103</v>
       </c>
       <c r="C6" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
